--- a/Data/EC/NIT-9007755635.xlsx
+++ b/Data/EC/NIT-9007755635.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Laura Wilches\Documents\2_ Macro Comfenalco Cartagena\Macro Aviso Incumplimiento y demás\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Operaciones\OneDrive - NIYARAKY COLOMBIA SAS OLD2\Escritorio\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D7A27C36-89E8-48DC-BBBE-B819729761D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BC675F4F-451E-4E0D-8503-AB5A2A34B408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{C53E97EA-8B45-4B10-AE55-B10DAD68DD93}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{AB2A53D6-CBCB-471C-A1B2-0D535FDF1DF6}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -584,22 +584,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>633769</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>55950</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>437794</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>125025</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{63528847-AA57-06AB-B59E-285CB5AF0779}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C7F4A7F-7F3B-F4B6-AE54-B0C2222951B6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -608,7 +608,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -621,7 +621,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="890944" y="236925"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -950,23 +950,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09B31E41-131C-415D-A31F-A2FCE79B2EFA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F798E209-52E6-49CA-B8D4-FA7AEA35C716}">
   <dimension ref="B2:J149"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.59765625" customWidth="1"/>
-    <col min="2" max="2" width="18.9296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.73046875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.59765625" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.59765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -979,7 +979,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -990,7 +990,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1001,7 +1001,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1012,8 +1012,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>50</v>
       </c>
@@ -1028,8 +1028,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1044,8 +1044,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>51</v>
       </c>
@@ -1060,8 +1060,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>52</v>
       </c>
@@ -1080,7 +1080,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1109,7 +1109,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1132,7 +1132,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1155,7 +1155,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1178,7 +1178,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1201,7 +1201,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1224,7 +1224,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1247,7 +1247,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1270,7 +1270,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1293,7 +1293,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1316,7 +1316,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1339,7 +1339,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1362,7 +1362,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1385,7 +1385,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1408,7 +1408,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1431,7 +1431,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1454,7 +1454,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1477,7 +1477,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1500,7 +1500,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1546,7 +1546,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1592,7 +1592,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1615,7 +1615,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1638,7 +1638,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1661,7 +1661,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1684,7 +1684,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1707,7 +1707,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1730,7 +1730,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1753,7 +1753,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1776,7 +1776,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1799,7 +1799,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1822,7 +1822,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1845,7 +1845,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1868,7 +1868,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1891,7 +1891,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1914,7 +1914,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -1937,7 +1937,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -1960,7 +1960,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -1983,7 +1983,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2006,7 +2006,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2029,7 +2029,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2052,7 +2052,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2075,7 +2075,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2098,7 +2098,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2121,7 +2121,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2144,7 +2144,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2167,7 +2167,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2190,7 +2190,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2213,7 +2213,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2236,7 +2236,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2259,7 +2259,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2282,7 +2282,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2305,7 +2305,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2328,7 +2328,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2351,7 +2351,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2374,7 +2374,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2397,7 +2397,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2420,7 +2420,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2443,7 +2443,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2466,7 +2466,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2489,7 +2489,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2512,7 +2512,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2535,7 +2535,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2558,7 +2558,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2581,7 +2581,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2604,7 +2604,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2627,7 +2627,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2650,7 +2650,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2673,7 +2673,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2719,7 +2719,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2742,7 +2742,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2765,7 +2765,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2788,7 +2788,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2811,7 +2811,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2834,7 +2834,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2857,7 +2857,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -2880,7 +2880,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -2903,7 +2903,7 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
@@ -2926,7 +2926,7 @@
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
@@ -2949,7 +2949,7 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
@@ -2972,7 +2972,7 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="15" t="s">
         <v>8</v>
       </c>
@@ -2995,7 +2995,7 @@
       <c r="I97" s="19"/>
       <c r="J97" s="20"/>
     </row>
-    <row r="98" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B98" s="15" t="s">
         <v>8</v>
       </c>
@@ -3018,7 +3018,7 @@
       <c r="I98" s="19"/>
       <c r="J98" s="20"/>
     </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B99" s="15" t="s">
         <v>8</v>
       </c>
@@ -3041,7 +3041,7 @@
       <c r="I99" s="19"/>
       <c r="J99" s="20"/>
     </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="15" t="s">
         <v>8</v>
       </c>
@@ -3064,7 +3064,7 @@
       <c r="I100" s="19"/>
       <c r="J100" s="20"/>
     </row>
-    <row r="101" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B101" s="15" t="s">
         <v>8</v>
       </c>
@@ -3087,7 +3087,7 @@
       <c r="I101" s="19"/>
       <c r="J101" s="20"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="15" t="s">
         <v>8</v>
       </c>
@@ -3110,7 +3110,7 @@
       <c r="I102" s="19"/>
       <c r="J102" s="20"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="15" t="s">
         <v>8</v>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="I103" s="19"/>
       <c r="J103" s="20"/>
     </row>
-    <row r="104" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B104" s="15" t="s">
         <v>8</v>
       </c>
@@ -3156,7 +3156,7 @@
       <c r="I104" s="19"/>
       <c r="J104" s="20"/>
     </row>
-    <row r="105" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B105" s="15" t="s">
         <v>8</v>
       </c>
@@ -3179,7 +3179,7 @@
       <c r="I105" s="19"/>
       <c r="J105" s="20"/>
     </row>
-    <row r="106" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B106" s="15" t="s">
         <v>8</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="I106" s="19"/>
       <c r="J106" s="20"/>
     </row>
-    <row r="107" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B107" s="15" t="s">
         <v>8</v>
       </c>
@@ -3225,7 +3225,7 @@
       <c r="I107" s="19"/>
       <c r="J107" s="20"/>
     </row>
-    <row r="108" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B108" s="15" t="s">
         <v>8</v>
       </c>
@@ -3248,7 +3248,7 @@
       <c r="I108" s="19"/>
       <c r="J108" s="20"/>
     </row>
-    <row r="109" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B109" s="15" t="s">
         <v>8</v>
       </c>
@@ -3271,7 +3271,7 @@
       <c r="I109" s="19"/>
       <c r="J109" s="20"/>
     </row>
-    <row r="110" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B110" s="15" t="s">
         <v>8</v>
       </c>
@@ -3294,7 +3294,7 @@
       <c r="I110" s="19"/>
       <c r="J110" s="20"/>
     </row>
-    <row r="111" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B111" s="15" t="s">
         <v>8</v>
       </c>
@@ -3317,7 +3317,7 @@
       <c r="I111" s="19"/>
       <c r="J111" s="20"/>
     </row>
-    <row r="112" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B112" s="15" t="s">
         <v>8</v>
       </c>
@@ -3340,7 +3340,7 @@
       <c r="I112" s="19"/>
       <c r="J112" s="20"/>
     </row>
-    <row r="113" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B113" s="15" t="s">
         <v>8</v>
       </c>
@@ -3363,7 +3363,7 @@
       <c r="I113" s="19"/>
       <c r="J113" s="20"/>
     </row>
-    <row r="114" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B114" s="15" t="s">
         <v>8</v>
       </c>
@@ -3386,7 +3386,7 @@
       <c r="I114" s="19"/>
       <c r="J114" s="20"/>
     </row>
-    <row r="115" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="115" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B115" s="15" t="s">
         <v>8</v>
       </c>
@@ -3409,7 +3409,7 @@
       <c r="I115" s="19"/>
       <c r="J115" s="20"/>
     </row>
-    <row r="116" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="116" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B116" s="15" t="s">
         <v>8</v>
       </c>
@@ -3432,7 +3432,7 @@
       <c r="I116" s="19"/>
       <c r="J116" s="20"/>
     </row>
-    <row r="117" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="117" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B117" s="15" t="s">
         <v>8</v>
       </c>
@@ -3455,7 +3455,7 @@
       <c r="I117" s="19"/>
       <c r="J117" s="20"/>
     </row>
-    <row r="118" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="118" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B118" s="15" t="s">
         <v>8</v>
       </c>
@@ -3478,7 +3478,7 @@
       <c r="I118" s="19"/>
       <c r="J118" s="20"/>
     </row>
-    <row r="119" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="119" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B119" s="15" t="s">
         <v>8</v>
       </c>
@@ -3501,7 +3501,7 @@
       <c r="I119" s="19"/>
       <c r="J119" s="20"/>
     </row>
-    <row r="120" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="120" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B120" s="15" t="s">
         <v>8</v>
       </c>
@@ -3524,7 +3524,7 @@
       <c r="I120" s="19"/>
       <c r="J120" s="20"/>
     </row>
-    <row r="121" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="121" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B121" s="15" t="s">
         <v>8</v>
       </c>
@@ -3547,7 +3547,7 @@
       <c r="I121" s="19"/>
       <c r="J121" s="20"/>
     </row>
-    <row r="122" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="122" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B122" s="15" t="s">
         <v>8</v>
       </c>
@@ -3570,7 +3570,7 @@
       <c r="I122" s="19"/>
       <c r="J122" s="20"/>
     </row>
-    <row r="123" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="123" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B123" s="15" t="s">
         <v>8</v>
       </c>
@@ -3593,7 +3593,7 @@
       <c r="I123" s="19"/>
       <c r="J123" s="20"/>
     </row>
-    <row r="124" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="124" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B124" s="15" t="s">
         <v>8</v>
       </c>
@@ -3616,7 +3616,7 @@
       <c r="I124" s="19"/>
       <c r="J124" s="20"/>
     </row>
-    <row r="125" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="125" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B125" s="15" t="s">
         <v>8</v>
       </c>
@@ -3639,7 +3639,7 @@
       <c r="I125" s="19"/>
       <c r="J125" s="20"/>
     </row>
-    <row r="126" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="126" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B126" s="15" t="s">
         <v>8</v>
       </c>
@@ -3662,7 +3662,7 @@
       <c r="I126" s="19"/>
       <c r="J126" s="20"/>
     </row>
-    <row r="127" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="127" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B127" s="15" t="s">
         <v>8</v>
       </c>
@@ -3685,7 +3685,7 @@
       <c r="I127" s="19"/>
       <c r="J127" s="20"/>
     </row>
-    <row r="128" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="128" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B128" s="15" t="s">
         <v>8</v>
       </c>
@@ -3708,7 +3708,7 @@
       <c r="I128" s="19"/>
       <c r="J128" s="20"/>
     </row>
-    <row r="129" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="129" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B129" s="15" t="s">
         <v>8</v>
       </c>
@@ -3731,7 +3731,7 @@
       <c r="I129" s="19"/>
       <c r="J129" s="20"/>
     </row>
-    <row r="130" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="130" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B130" s="15" t="s">
         <v>8</v>
       </c>
@@ -3754,7 +3754,7 @@
       <c r="I130" s="19"/>
       <c r="J130" s="20"/>
     </row>
-    <row r="131" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="131" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B131" s="15" t="s">
         <v>8</v>
       </c>
@@ -3777,7 +3777,7 @@
       <c r="I131" s="19"/>
       <c r="J131" s="20"/>
     </row>
-    <row r="132" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="132" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B132" s="15" t="s">
         <v>8</v>
       </c>
@@ -3800,7 +3800,7 @@
       <c r="I132" s="19"/>
       <c r="J132" s="20"/>
     </row>
-    <row r="133" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="133" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B133" s="15" t="s">
         <v>8</v>
       </c>
@@ -3823,7 +3823,7 @@
       <c r="I133" s="19"/>
       <c r="J133" s="20"/>
     </row>
-    <row r="134" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="134" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B134" s="15" t="s">
         <v>8</v>
       </c>
@@ -3846,7 +3846,7 @@
       <c r="I134" s="19"/>
       <c r="J134" s="20"/>
     </row>
-    <row r="135" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="135" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B135" s="15" t="s">
         <v>8</v>
       </c>
@@ -3869,7 +3869,7 @@
       <c r="I135" s="19"/>
       <c r="J135" s="20"/>
     </row>
-    <row r="136" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="136" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B136" s="15" t="s">
         <v>8</v>
       </c>
@@ -3892,7 +3892,7 @@
       <c r="I136" s="19"/>
       <c r="J136" s="20"/>
     </row>
-    <row r="137" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="137" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B137" s="15" t="s">
         <v>8</v>
       </c>
@@ -3915,7 +3915,7 @@
       <c r="I137" s="19"/>
       <c r="J137" s="20"/>
     </row>
-    <row r="138" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="138" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B138" s="15" t="s">
         <v>8</v>
       </c>
@@ -3938,7 +3938,7 @@
       <c r="I138" s="19"/>
       <c r="J138" s="20"/>
     </row>
-    <row r="139" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="139" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B139" s="15" t="s">
         <v>8</v>
       </c>
@@ -3961,7 +3961,7 @@
       <c r="I139" s="19"/>
       <c r="J139" s="20"/>
     </row>
-    <row r="140" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="140" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B140" s="15" t="s">
         <v>8</v>
       </c>
@@ -3984,7 +3984,7 @@
       <c r="I140" s="19"/>
       <c r="J140" s="20"/>
     </row>
-    <row r="141" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="141" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B141" s="15" t="s">
         <v>8</v>
       </c>
@@ -4007,7 +4007,7 @@
       <c r="I141" s="19"/>
       <c r="J141" s="20"/>
     </row>
-    <row r="142" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="142" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B142" s="15" t="s">
         <v>8</v>
       </c>
@@ -4030,7 +4030,7 @@
       <c r="I142" s="19"/>
       <c r="J142" s="20"/>
     </row>
-    <row r="143" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="143" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B143" s="21" t="s">
         <v>8</v>
       </c>
@@ -4053,7 +4053,7 @@
       <c r="I143" s="25"/>
       <c r="J143" s="26"/>
     </row>
-    <row r="148" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="148" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B148" s="32" t="s">
         <v>58</v>
       </c>
@@ -4064,7 +4064,7 @@
       <c r="I148" s="1"/>
       <c r="J148" s="1"/>
     </row>
-    <row r="149" spans="2:10" x14ac:dyDescent="0.45">
+    <row r="149" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B149" s="32" t="s">
         <v>57</v>
       </c>
